--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513650_FASEFINALAFFA1_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513650_FASEFINALAFFA1_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5214</v>
+        <v>5.5068</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2572</v>
+        <v>4.02</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2642</v>
+        <v>1.4868</v>
       </c>
       <c r="G2" t="n">
         <v>2.2593</v>
@@ -610,13 +610,13 @@
         <v>1.7526</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2301</v>
+        <v>1.2155</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.6867</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3062</v>
+        <v>0.5288</v>
       </c>
       <c r="V2" t="n">
         <v>0.2795</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9857</v>
+        <v>4.7198</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9639</v>
+        <v>3.0876</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0218</v>
+        <v>1.6322</v>
       </c>
       <c r="G3" t="n">
         <v>0.6178</v>
@@ -688,13 +688,13 @@
         <v>1.7526</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3942</v>
+        <v>1.1283</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1265</v>
+        <v>0.2501</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2677</v>
+        <v>0.8781</v>
       </c>
       <c r="V3" t="n">
         <v>1.2211</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6089</v>
+        <v>3.6429</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8722</v>
+        <v>1.9341</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7367</v>
+        <v>1.7089</v>
       </c>
       <c r="G4" t="n">
         <v>3.5394</v>
@@ -766,13 +766,13 @@
         <v>0.7789</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0988</v>
+        <v>-0.0648</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2538</v>
+        <v>-0.192</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1549</v>
+        <v>0.1271</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6105</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8585</v>
+        <v>2.7812</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4348</v>
+        <v>1.4966</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4238</v>
+        <v>1.2846</v>
       </c>
       <c r="G5" t="n">
         <v>2.0019</v>
@@ -844,13 +844,13 @@
         <v>0.3895</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1361</v>
+        <v>0.0588</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2473</v>
+        <v>-0.1855</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3835</v>
+        <v>0.2443</v>
       </c>
       <c r="V5" t="n">
         <v>0.3311</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ FLORES</t>
+          <t>A. MEJIA BERIGUETE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.604</v>
+        <v>2.5395</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1353</v>
+        <v>0.0969</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4687</v>
+        <v>2.4425</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7353</v>
+        <v>1.8323</v>
       </c>
       <c r="H6" t="n">
-        <v>1.345</v>
+        <v>2.691</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6097</v>
+        <v>-0.8588</v>
       </c>
       <c r="J6" t="n">
-        <v>0.797</v>
+        <v>1.1755</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3805</v>
+        <v>2.666</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5835</v>
+        <v>-1.4905</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0617</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0355</v>
+        <v>0.0251</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0262</v>
+        <v>0.6317</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7789</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.921</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7789</v>
+        <v>2.1421</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0898</v>
+        <v>-0.3454</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6617</v>
+        <v>-0.2685</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7514999999999999</v>
+        <v>-0.0769</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.8316</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.1111</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MEJIA BERIGUETE</t>
+          <t>I. VAZQUEZ FLORES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3858</v>
+        <v>1.9316</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.862</v>
+        <v>0.6577</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2478</v>
+        <v>1.274</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8323</v>
+        <v>0.7353</v>
       </c>
       <c r="H7" t="n">
-        <v>2.691</v>
+        <v>1.345</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8588</v>
+        <v>-0.6097</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1755</v>
+        <v>0.797</v>
       </c>
       <c r="K7" t="n">
-        <v>2.666</v>
+        <v>1.3805</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4905</v>
+        <v>-0.5835</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6568000000000001</v>
+        <v>-0.0617</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0251</v>
+        <v>-0.0355</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6317</v>
+        <v>-0.0262</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7789</v>
+        <v>0.7789</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.921</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1421</v>
+        <v>0.7789</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4991</v>
+        <v>0.4174</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2275</v>
+        <v>-0.1393</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2716</v>
+        <v>0.5567</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8316</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1111</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0163</v>
+        <v>0.9121</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2035</v>
+        <v>-0.0955</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8128</v>
+        <v>1.0076</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0142</v>
@@ -1156,13 +1156,13 @@
         <v>0.1947</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5563</v>
+        <v>0.452</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4449</v>
+        <v>0.1458</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1114</v>
+        <v>0.3062</v>
       </c>
       <c r="V9" t="n">
         <v>0.2795</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5982</v>
+        <v>0.2045</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0227</v>
+        <v>-0.5205</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4245</v>
+        <v>0.725</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9997</v>
+        <v>-3.2356</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4485</v>
+        <v>-2.0227</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5513</v>
+        <v>-1.2128</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0463</v>
+        <v>-2.9371</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0463</v>
+        <v>-1.7702</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.1669</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.046</v>
+        <v>-0.2985</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4947</v>
+        <v>-0.2526</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5513</v>
+        <v>-0.0459</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1947</v>
+        <v>2.1421</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1947</v>
+        <v>2.1421</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4032</v>
+        <v>0.4079</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9765</v>
+        <v>0.3055</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4267</v>
+        <v>0.1024</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.1111</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. ALOGO EVUNA</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2104</v>
+        <v>-0.0053</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4502</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6605</v>
+        <v>-0.5915</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6147</v>
+        <v>-0.9997</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2303</v>
+        <v>-0.4485</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3844</v>
+        <v>-0.5513</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6136</v>
+        <v>0.0463</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0104</v>
+        <v>0.0463</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.624</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0012</v>
+        <v>-1.046</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2407</v>
+        <v>-0.4947</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2396</v>
+        <v>-0.5513</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1947</v>
+        <v>0.1947</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7789</v>
+        <v>0.1947</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0198</v>
+        <v>0.7997</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1371</v>
+        <v>0.5399</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1172</v>
+        <v>0.2598</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>R. ALOGO EVUNA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1418</v>
+        <v>-0.4842</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6442</v>
+        <v>-1.423</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5024</v>
+        <v>0.9388</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.2356</v>
+        <v>-0.6147</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.0227</v>
+        <v>-0.2303</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2128</v>
+        <v>-0.3844</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.9371</v>
+        <v>-0.6136</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.7702</v>
+        <v>0.0104</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1669</v>
+        <v>-0.624</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2985</v>
+        <v>-0.0012</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2526</v>
+        <v>-0.2407</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0459</v>
+        <v>0.2396</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1421</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1421</v>
+        <v>0.7789</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0617</v>
+        <v>0.3253</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1818</v>
+        <v>0.1643</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1202</v>
+        <v>0.161</v>
       </c>
       <c r="V12" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.1111</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.4048</v>
+        <v>-0.5788</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1506</v>
+        <v>-2.1299</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7459</v>
+        <v>1.5511</v>
       </c>
       <c r="G13" t="n">
         <v>-2.773</v>
@@ -1468,13 +1468,13 @@
         <v>1.7526</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3523</v>
+        <v>0.4737</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9709</v>
+        <v>0.0499</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6186</v>
+        <v>0.4238</v>
       </c>
       <c r="V13" t="n">
         <v>0.9416</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.4663</v>
+        <v>22.3938</v>
       </c>
       <c r="E14" t="n">
-        <v>8.0063</v>
+        <v>8.933899999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>13.4601</v>
+        <v>13.46</v>
       </c>
       <c r="G14" t="n">
         <v>4.5725</v>
@@ -1522,7 +1522,7 @@
         <v>5.222300000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>7.051999999999999</v>
+        <v>7.052</v>
       </c>
       <c r="L14" t="n">
         <v>-1.8295</v>
@@ -1546,13 +1546,13 @@
         <v>12.6576</v>
       </c>
       <c r="S14" t="n">
-        <v>3.941</v>
+        <v>4.8684</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4295000000000001</v>
+        <v>1.3569</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5115</v>
+        <v>3.5113</v>
       </c>
       <c r="V14" t="n">
         <v>5.1639</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.07</v>
+        <v>1.1103</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7754</v>
+        <v>0.3766</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2946</v>
+        <v>0.7336</v>
       </c>
       <c r="G16" t="n">
         <v>0.07140000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>0.3895</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2103</v>
+        <v>-0.17</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1172</v>
+        <v>-0.2815</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3275</v>
+        <v>0.1114</v>
       </c>
       <c r="V16" t="n">
         <v>0.8195</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. CERVANTES GUERRA</t>
+          <t>D. MARTÍNEZ JURADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7659</v>
+        <v>0.6079</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1788</v>
+        <v>0.6079</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4129</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2695</v>
+        <v>0.6079</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6174</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8869</v>
+        <v>0.6079</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6799</v>
+        <v>0.6079</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9543</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6342</v>
+        <v>0.6079</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4104</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6631</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2527</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5842000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1684</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5842000000000001</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7032</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6673</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.036</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.6226</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. MARTÍNEZ JURADO</t>
+          <t>G. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6079</v>
+        <v>0.3967</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6079</v>
+        <v>-0.0858</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.4825</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6079</v>
+        <v>0.1934</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6079</v>
+        <v>0.3987</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6079</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6079</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.1934</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.3987</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.1306</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.0858</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.2164</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.1221</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. FONT FENOLLAR</t>
+          <t>L. CERVANTES GUERRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3526</v>
+        <v>-0.0834</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1855</v>
+        <v>0.481</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5381</v>
+        <v>-0.5645</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1934</v>
+        <v>1.2695</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2053</v>
+        <v>-1.6174</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3987</v>
+        <v>2.8869</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.6799</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.9543</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.6342</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1934</v>
+        <v>-0.4104</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2053</v>
+        <v>-0.6631</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3987</v>
+        <v>0.2527</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1947</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1684</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1947</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0866</v>
+        <v>0.8539</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1855</v>
+        <v>-0.0304</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2721</v>
+        <v>0.8844</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1221</v>
+        <v>-1.6226</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1221</v>
+        <v>-1.6226</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6198</v>
+        <v>-0.6339</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8843</v>
+        <v>1.0836</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5041</v>
+        <v>-1.7176</v>
       </c>
       <c r="G20" t="n">
         <v>1.8732</v>
@@ -2014,13 +2014,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2346</v>
+        <v>-0.2487</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6248</v>
+        <v>-0.4254</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3902</v>
+        <v>0.1767</v>
       </c>
       <c r="V20" t="n">
         <v>-1.6742</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4555</v>
+        <v>-0.968</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2034</v>
+        <v>-1.9044</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7479</v>
+        <v>0.9364</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4942</v>
@@ -2092,13 +2092,13 @@
         <v>0.3895</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2287</v>
+        <v>0.2589</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3525</v>
+        <v>-0.0535</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1238</v>
+        <v>0.3124</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1221</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.596</v>
+        <v>-1.2861</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7865</v>
+        <v>-0.6868</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8095</v>
+        <v>-0.5994</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2931</v>
@@ -2170,13 +2170,13 @@
         <v>0.1947</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4976</v>
+        <v>-0.1878</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3867</v>
+        <v>-0.287</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.111</v>
+        <v>0.0992</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>A. LOPEZ ALVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8087</v>
+        <v>-1.4494</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7165</v>
+        <v>-3.0311</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.09229999999999999</v>
+        <v>1.5817</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.852</v>
+        <v>-0.6968</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6071</v>
+        <v>-0.1294</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.245</v>
+        <v>-0.5674</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0611</v>
+        <v>-1.6272</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0205</v>
+        <v>-0.5413</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0405</v>
+        <v>-1.0859</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9131</v>
+        <v>0.9304</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6276</v>
+        <v>0.4119</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2855</v>
+        <v>0.5185</v>
       </c>
       <c r="P23" t="n">
         <v>-0.3895</v>
@@ -2248,28 +2248,28 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4451</v>
+        <v>-0.3632</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7097</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3587</v>
+        <v>0.3465</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1221</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1221</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. LOPEZ ALVAREZ-TIRADOR</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,40 +2281,40 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1031</v>
+        <v>-1.6596</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2305</v>
+        <v>-1.6168</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1273</v>
+        <v>-0.0428</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6968</v>
+        <v>-0.852</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1294</v>
+        <v>-0.6071</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5674</v>
+        <v>-0.245</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.6272</v>
+        <v>0.0611</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5413</v>
+        <v>0.0205</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.0859</v>
+        <v>0.0405</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9304</v>
+        <v>-0.9131</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4119</v>
+        <v>-0.6276</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5185</v>
+        <v>-0.2855</v>
       </c>
       <c r="P24" t="n">
         <v>-0.3895</v>
@@ -2326,22 +2326,22 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0169</v>
+        <v>-0.296</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9091</v>
+        <v>-0.7042</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1078</v>
+        <v>0.4082</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.1221</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2795</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.4016</v>
+        <v>-1.6636</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.1322</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2693</v>
+        <v>-0.8303</v>
       </c>
       <c r="G25" t="n">
         <v>0.4717</v>
@@ -2404,13 +2404,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9459</v>
+        <v>-0.2079</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7854</v>
+        <v>-0.4864</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1605</v>
+        <v>0.2785</v>
       </c>
       <c r="V25" t="n">
         <v>-1.3432</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.7965</v>
+        <v>-3.9518</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.9957</v>
+        <v>-4.494</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1992</v>
+        <v>0.5422</v>
       </c>
       <c r="G26" t="n">
         <v>-2.647</v>
@@ -2482,13 +2482,13 @@
         <v>0.1947</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2721</v>
+        <v>0.1167</v>
       </c>
       <c r="T26" t="n">
-        <v>0.587</v>
+        <v>0.0886</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3149</v>
+        <v>0.0281</v>
       </c>
       <c r="V26" t="n">
         <v>0.3311</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.4822</v>
+        <v>-4.0456</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.81</v>
+        <v>-2.1123</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.6722</v>
+        <v>-1.9334</v>
       </c>
       <c r="G27" t="n">
         <v>-2.2934</v>
@@ -2560,13 +2560,13 @@
         <v>0.3895</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.4451</v>
+        <v>-1.0085</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.3604</v>
+        <v>-0.6626</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.0847</v>
+        <v>-0.3459</v>
       </c>
       <c r="V27" t="n">
         <v>0.0353</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-6.8309</v>
+        <v>-7.0132</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.6776</v>
+        <v>-3.0763</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.1533</v>
+        <v>-3.9369</v>
       </c>
       <c r="G28" t="n">
         <v>-1.6145</v>
@@ -2638,13 +2638,13 @@
         <v>0.1947</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0215</v>
+        <v>-0.1608</v>
       </c>
       <c r="T28" t="n">
-        <v>0.5252</v>
+        <v>0.1265</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.5036</v>
+        <v>-0.2873</v>
       </c>
       <c r="V28" t="n">
         <v>-1.3432</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-21.4663</v>
+        <v>-18.8081</v>
       </c>
       <c r="E29" t="n">
-        <v>-13.4599</v>
+        <v>-13.46</v>
       </c>
       <c r="F29" t="n">
-        <v>-8.006499999999999</v>
+        <v>-5.3485</v>
       </c>
       <c r="G29" t="n">
         <v>-4.5723</v>
@@ -2689,7 +2689,7 @@
         <v>2.124599999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0.649999999999999</v>
+        <v>0.6499999999999995</v>
       </c>
       <c r="K29" t="n">
         <v>0.3549000000000002</v>
@@ -2716,13 +2716,13 @@
         <v>4.868300000000001</v>
       </c>
       <c r="S29" t="n">
-        <v>-3.9408</v>
+        <v>-1.2828</v>
       </c>
       <c r="T29" t="n">
-        <v>-3.5116</v>
+        <v>-3.5114</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.4292</v>
+        <v>2.2286</v>
       </c>
       <c r="V29" t="n">
         <v>-5.1636</v>
